--- a/LISTAS/ma/BULON CABEZA REDONDA DISMAY.xlsx
+++ b/LISTAS/ma/BULON CABEZA REDONDA DISMAY.xlsx
@@ -728,7 +728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75"/>
   <cols>
     <col width="16" customWidth="1" style="20" min="1" max="1"/>
@@ -739,14 +739,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45163.60836888417</v>
+        <v>45219</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="20">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -768,8 +764,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11" ht="41.25" customHeight="1" s="20">
       <c r="A11" s="21" t="inlineStr">
         <is>
@@ -784,8 +778,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14"/>
     <row r="15" ht="24.75" customHeight="1" s="20">
       <c r="A15" s="23" t="inlineStr">
         <is>
@@ -793,8 +785,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17"/>
     <row r="18" ht="18" customHeight="1" s="20">
       <c r="A18" s="8" t="inlineStr">
         <is>
@@ -844,7 +834,7 @@
       </c>
       <c r="C20" s="18" t="n"/>
       <c r="D20" s="7" t="n">
-        <v>1670.038</v>
+        <v>1700</v>
       </c>
       <c r="E20" s="3" t="n"/>
     </row>
@@ -1027,7 +1017,6 @@
         <v>5389.681</v>
       </c>
     </row>
-    <row r="32"/>
     <row r="33" ht="15.75" customHeight="1" s="20"/>
     <row r="34" ht="23.25" customHeight="1" s="20">
       <c r="A34" s="23" t="inlineStr">
@@ -1036,8 +1025,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36"/>
     <row r="37" ht="18" customHeight="1" s="20">
       <c r="A37" s="8" t="inlineStr">
         <is>
@@ -1200,8 +1187,6 @@
         <v>8722.165999999999</v>
       </c>
     </row>
-    <row r="47"/>
-    <row r="48"/>
     <row r="49" ht="24.75" customHeight="1" s="20">
       <c r="B49" s="23" t="inlineStr">
         <is>
@@ -1209,8 +1194,6 @@
         </is>
       </c>
     </row>
-    <row r="50"/>
-    <row r="51"/>
     <row r="52" ht="18" customHeight="1" s="20">
       <c r="A52" s="8" t="inlineStr">
         <is>
@@ -1421,52 +1404,51 @@
         <v>9033.405000000001</v>
       </c>
     </row>
-    <row r="65"/>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B26:C26"/>
     <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B27:C27"/>
     <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B18:C18"/>
     <mergeCell ref="A34:D34"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
     <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B62:C62"/>
     <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B56:C56"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/BULON CABEZA REDONDA DISMAY.xlsx
+++ b/LISTAS/ma/BULON CABEZA REDONDA DISMAY.xlsx
@@ -739,7 +739,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45219</v>
+        <v>45237</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/ma/BULON CABEZA REDONDA DISMAY.xlsx
+++ b/LISTAS/ma/BULON CABEZA REDONDA DISMAY.xlsx
@@ -739,7 +739,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45237</v>
+        <v>45238</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
@@ -1406,49 +1406,49 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="B62:C62"/>
     <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B25:C25"/>
     <mergeCell ref="B59:C59"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B41:C41"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B45:C45"/>
     <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B43:C43"/>
     <mergeCell ref="B58:C58"/>
     <mergeCell ref="B39:C39"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="A12:D12"/>
     <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="A34:D34"/>
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B44:C44"/>
     <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B19:C19"/>
     <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B45:C45"/>
     <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B41:C41"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/BULON CABEZA REDONDA DISMAY.xlsx
+++ b/LISTAS/ma/BULON CABEZA REDONDA DISMAY.xlsx
@@ -739,7 +739,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45238</v>
+        <v>45239</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/ma/BULON CABEZA REDONDA DISMAY.xlsx
+++ b/LISTAS/ma/BULON CABEZA REDONDA DISMAY.xlsx
@@ -1406,49 +1406,49 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="B62:C62"/>
     <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="B49:E49"/>
     <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B20:C20"/>
     <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="B26:C26"/>
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="B23:C23"/>
-    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
     <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B24:C24"/>
     <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B56:C56"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/BULON CABEZA REDONDA DISMAY.xlsx
+++ b/LISTAS/ma/BULON CABEZA REDONDA DISMAY.xlsx
@@ -739,7 +739,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45239</v>
+        <v>45244</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/ma/BULON CABEZA REDONDA DISMAY.xlsx
+++ b/LISTAS/ma/BULON CABEZA REDONDA DISMAY.xlsx
@@ -739,7 +739,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45244</v>
+        <v>45251</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/ma/BULON CABEZA REDONDA DISMAY.xlsx
+++ b/LISTAS/ma/BULON CABEZA REDONDA DISMAY.xlsx
@@ -739,7 +739,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45251</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
@@ -1406,49 +1406,49 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="B62:C62"/>
     <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B25:C25"/>
     <mergeCell ref="B59:C59"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B41:C41"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B45:C45"/>
     <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B43:C43"/>
     <mergeCell ref="B58:C58"/>
     <mergeCell ref="B39:C39"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="A12:D12"/>
     <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="A34:D34"/>
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="B23:C23"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B45:C45"/>
     <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B41:C41"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/BULON CABEZA REDONDA DISMAY.xlsx
+++ b/LISTAS/ma/BULON CABEZA REDONDA DISMAY.xlsx
@@ -739,7 +739,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45253</v>
+        <v>45254</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
@@ -1406,49 +1406,49 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="B62:C62"/>
     <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B25:C25"/>
     <mergeCell ref="B59:C59"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B41:C41"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B45:C45"/>
     <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B43:C43"/>
     <mergeCell ref="B58:C58"/>
     <mergeCell ref="B39:C39"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="A12:D12"/>
     <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="A34:D34"/>
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="B23:C23"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B45:C45"/>
     <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B41:C41"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/BULON CABEZA REDONDA DISMAY.xlsx
+++ b/LISTAS/ma/BULON CABEZA REDONDA DISMAY.xlsx
@@ -739,7 +739,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45254</v>
+        <v>45255</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
@@ -1406,49 +1406,49 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="B62:C62"/>
     <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B25:C25"/>
     <mergeCell ref="B59:C59"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B41:C41"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B45:C45"/>
     <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B43:C43"/>
     <mergeCell ref="B58:C58"/>
     <mergeCell ref="B39:C39"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="A12:D12"/>
     <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="A34:D34"/>
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="B23:C23"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B45:C45"/>
     <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B41:C41"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/BULON CABEZA REDONDA DISMAY.xlsx
+++ b/LISTAS/ma/BULON CABEZA REDONDA DISMAY.xlsx
@@ -739,7 +739,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45255</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/ma/BULON CABEZA REDONDA DISMAY.xlsx
+++ b/LISTAS/ma/BULON CABEZA REDONDA DISMAY.xlsx
@@ -739,7 +739,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/ma/BULON CABEZA REDONDA DISMAY.xlsx
+++ b/LISTAS/ma/BULON CABEZA REDONDA DISMAY.xlsx
@@ -728,7 +728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75"/>
   <cols>
     <col width="16" customWidth="1" style="20" min="1" max="1"/>
@@ -739,10 +739,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45266</v>
+        <v>45264.5480686345</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="20">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -764,6 +768,8 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
+    <row r="10"/>
     <row r="11" ht="41.25" customHeight="1" s="20">
       <c r="A11" s="21" t="inlineStr">
         <is>
@@ -778,6 +784,8 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14"/>
     <row r="15" ht="24.75" customHeight="1" s="20">
       <c r="A15" s="23" t="inlineStr">
         <is>
@@ -785,6 +793,8 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18" ht="18" customHeight="1" s="20">
       <c r="A18" s="8" t="inlineStr">
         <is>
@@ -817,7 +827,7 @@
       </c>
       <c r="C19" s="18" t="n"/>
       <c r="D19" s="7" t="n">
-        <v>1577.056</v>
+        <v>2022.06</v>
       </c>
       <c r="E19" s="13" t="n"/>
     </row>
@@ -834,7 +844,7 @@
       </c>
       <c r="C20" s="18" t="n"/>
       <c r="D20" s="7" t="n">
-        <v>1700</v>
+        <v>2141.28</v>
       </c>
       <c r="E20" s="3" t="n"/>
     </row>
@@ -851,7 +861,7 @@
       </c>
       <c r="C21" s="18" t="n"/>
       <c r="D21" s="7" t="n">
-        <v>1875.005</v>
+        <v>2404.08</v>
       </c>
       <c r="E21" s="3" t="n"/>
     </row>
@@ -868,7 +878,7 @@
       </c>
       <c r="C22" s="18" t="n"/>
       <c r="D22" s="7" t="n">
-        <v>2079.958</v>
+        <v>2666.87</v>
       </c>
       <c r="E22" s="3" t="n"/>
     </row>
@@ -885,7 +895,7 @@
       </c>
       <c r="C23" s="18" t="n"/>
       <c r="D23" s="7" t="n">
-        <v>2326.669</v>
+        <v>2983.2</v>
       </c>
       <c r="E23" s="3" t="n"/>
     </row>
@@ -902,7 +912,7 @@
       </c>
       <c r="C24" s="18" t="n"/>
       <c r="D24" s="7" t="n">
-        <v>2512.655</v>
+        <v>3221.66</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1" s="20">
@@ -918,7 +928,7 @@
       </c>
       <c r="C25" s="18" t="n"/>
       <c r="D25" s="7" t="n">
-        <v>2782.138</v>
+        <v>3567.19</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1" s="20">
@@ -934,7 +944,7 @@
       </c>
       <c r="C26" s="18" t="n"/>
       <c r="D26" s="7" t="n">
-        <v>2952.936</v>
+        <v>3786.18</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1" s="20">
@@ -950,7 +960,7 @@
       </c>
       <c r="C27" s="18" t="n"/>
       <c r="D27" s="7" t="n">
-        <v>3264.171</v>
+        <v>4185.24</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="20">
@@ -966,7 +976,7 @@
       </c>
       <c r="C28" s="18" t="n"/>
       <c r="D28" s="7" t="n">
-        <v>3666.498</v>
+        <v>4701.09</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1" s="20">
@@ -982,7 +992,7 @@
       </c>
       <c r="C29" s="18" t="n"/>
       <c r="D29" s="7" t="n">
-        <v>4061.241</v>
+        <v>5207.22</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1" s="20">
@@ -998,7 +1008,7 @@
       </c>
       <c r="C30" s="18" t="n"/>
       <c r="D30" s="7" t="n">
-        <v>4592.616</v>
+        <v>5888.54</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1" s="20">
@@ -1014,9 +1024,10 @@
       </c>
       <c r="C31" s="18" t="n"/>
       <c r="D31" s="7" t="n">
-        <v>5389.681</v>
-      </c>
-    </row>
+        <v>6910.52</v>
+      </c>
+    </row>
+    <row r="32"/>
     <row r="33" ht="15.75" customHeight="1" s="20"/>
     <row r="34" ht="23.25" customHeight="1" s="20">
       <c r="A34" s="23" t="inlineStr">
@@ -1025,6 +1036,8 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
+    <row r="36"/>
     <row r="37" ht="18" customHeight="1" s="20">
       <c r="A37" s="8" t="inlineStr">
         <is>
@@ -1056,7 +1069,7 @@
       </c>
       <c r="C38" s="18" t="n"/>
       <c r="D38" s="7" t="n">
-        <v>5549.094</v>
+        <v>7114.91</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1" s="20">
@@ -1072,7 +1085,7 @@
       </c>
       <c r="C39" s="18" t="n"/>
       <c r="D39" s="7" t="n">
-        <v>6543.529</v>
+        <v>8389.950000000001</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1" s="20">
@@ -1088,7 +1101,7 @@
       </c>
       <c r="C40" s="18" t="n"/>
       <c r="D40" s="7" t="n">
-        <v>7629.048</v>
+        <v>9781.780000000001</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1" s="20">
@@ -1104,7 +1117,7 @@
       </c>
       <c r="C41" s="18" t="n"/>
       <c r="D41" s="7" t="n">
-        <v>9644.49</v>
+        <v>12365.93</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1" s="20">
@@ -1120,7 +1133,7 @@
       </c>
       <c r="C42" s="18" t="n"/>
       <c r="D42" s="7" t="n">
-        <v>12400.054</v>
+        <v>15899.05</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1" s="20">
@@ -1136,7 +1149,7 @@
       </c>
       <c r="C43" s="18" t="n"/>
       <c r="D43" s="7" t="n">
-        <v>15265.698</v>
+        <v>19573.31</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1" s="20">
@@ -1152,7 +1165,7 @@
       </c>
       <c r="C44" s="18" t="n"/>
       <c r="D44" s="7" t="n">
-        <v>17269.749</v>
+        <v>22142.85</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1" s="20">
@@ -1168,7 +1181,7 @@
       </c>
       <c r="C45" s="18" t="n"/>
       <c r="D45" s="7" t="n">
-        <v>19850.719</v>
+        <v>25452.11</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1" s="20">
@@ -1184,9 +1197,11 @@
       </c>
       <c r="C46" s="18" t="n"/>
       <c r="D46" s="7" t="n">
-        <v>8722.165999999999</v>
-      </c>
-    </row>
+        <v>11183.35</v>
+      </c>
+    </row>
+    <row r="47"/>
+    <row r="48"/>
     <row r="49" ht="24.75" customHeight="1" s="20">
       <c r="B49" s="23" t="inlineStr">
         <is>
@@ -1194,6 +1209,8 @@
         </is>
       </c>
     </row>
+    <row r="50"/>
+    <row r="51"/>
     <row r="52" ht="18" customHeight="1" s="20">
       <c r="A52" s="8" t="inlineStr">
         <is>
@@ -1225,7 +1242,7 @@
       </c>
       <c r="C53" s="18" t="n"/>
       <c r="D53" s="7" t="n">
-        <v>2728.997</v>
+        <v>3499.05</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1" s="20">
@@ -1241,7 +1258,7 @@
       </c>
       <c r="C54" s="18" t="n"/>
       <c r="D54" s="7" t="n">
-        <v>3279.351</v>
+        <v>4204.7</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1" s="20">
@@ -1257,7 +1274,7 @@
       </c>
       <c r="C55" s="18" t="n"/>
       <c r="D55" s="7" t="n">
-        <v>3518.47</v>
+        <v>4511.29</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1" s="20">
@@ -1273,7 +1290,7 @@
       </c>
       <c r="C56" s="18" t="n"/>
       <c r="D56" s="7" t="n">
-        <v>3992.921</v>
+        <v>5119.62</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1" s="20">
@@ -1289,7 +1306,7 @@
       </c>
       <c r="C57" s="18" t="n"/>
       <c r="D57" s="7" t="n">
-        <v>4343.178</v>
+        <v>5568.72</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1" s="20">
@@ -1305,7 +1322,7 @@
       </c>
       <c r="C58" s="18" t="n"/>
       <c r="D58" s="7" t="n">
-        <v>4687.502</v>
+        <v>6010.2</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1" s="20">
@@ -1321,7 +1338,7 @@
       </c>
       <c r="C59" s="18" t="n"/>
       <c r="D59" s="7" t="n">
-        <v>5082.241</v>
+        <v>6516.32</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1" s="20">
@@ -1337,7 +1354,7 @@
       </c>
       <c r="C60" s="18" t="n"/>
       <c r="D60" s="7" t="n">
-        <v>5241.652</v>
+        <v>6720.72</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1" s="20">
@@ -1353,7 +1370,7 @@
       </c>
       <c r="C61" s="18" t="n"/>
       <c r="D61" s="7" t="n">
-        <v>5723.682</v>
+        <v>7338.76</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1" s="20">
@@ -1369,7 +1386,7 @@
       </c>
       <c r="C62" s="18" t="n"/>
       <c r="D62" s="7" t="n">
-        <v>6786.445</v>
+        <v>8701.41</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1" s="20">
@@ -1385,7 +1402,7 @@
       </c>
       <c r="C63" s="18" t="n"/>
       <c r="D63" s="7" t="n">
-        <v>7325.414</v>
+        <v>9392.469999999999</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1" s="20">
@@ -1401,54 +1418,55 @@
       </c>
       <c r="C64" s="18" t="n"/>
       <c r="D64" s="7" t="n">
-        <v>9033.405000000001</v>
-      </c>
-    </row>
+        <v>11582.41</v>
+      </c>
+    </row>
+    <row r="65"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B21:C21"/>
     <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B64:C64"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
     <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B41:C41"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>
